--- a/data/trans_camb/P19C08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,2</t>
+          <t>-0,31; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,51</t>
+          <t>-0,48; 1,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; -0,13</t>
+          <t>-1,24; -0,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,45</t>
+          <t>-0,82; 0,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,63</t>
+          <t>-0,81; 0,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,14</t>
+          <t>-0,98; 0,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,59</t>
+          <t>-0,44; 0,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,6</t>
+          <t>-0,48; 0,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; -0,02</t>
+          <t>-0,79; -0,03</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,1; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 302,39</t>
+          <t>-100,0; 248,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 365,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,77; 108,76</t>
+          <t>-97,69; 80,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 286,52</t>
+          <t>-65,55; 239,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 237,64</t>
+          <t>-75,31; 296,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-96,88; 10,85</t>
+          <t>-94,94; 38,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,06</t>
+          <t>0,12; 1,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,0</t>
+          <t>-0,37; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,08</t>
+          <t>0,18; 1,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,95</t>
+          <t>-0,28; 0,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; -0,1</t>
+          <t>-0,94; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,18</t>
+          <t>-0,76; 0,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,82</t>
+          <t>0,05; 0,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; -0,08</t>
+          <t>-0,53; -0,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,48</t>
+          <t>-0,14; 0,47</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 463,2</t>
+          <t>-49,36; 389,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,16; 104,46</t>
+          <t>-81,68; 103,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 569,52</t>
+          <t>-0,04; 603,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 331,66</t>
+          <t>-38,43; 359,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,93</t>
+          <t>-1,53; 0,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,03</t>
+          <t>-2,05; 0,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,13</t>
+          <t>-1,78; 0,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,64</t>
+          <t>-1,59; 0,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,82</t>
+          <t>-1,46; 0,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,05</t>
+          <t>-1,09; 1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,38</t>
+          <t>-1,06; 0,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,16</t>
+          <t>-1,23; 0,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,38</t>
+          <t>-1,17; 0,34</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 279,42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-99,76; 203,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,75; —</t>
+          <t>-80,34; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 80,87</t>
+          <t>-82,37; 102,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-91,0; 123,45</t>
+          <t>-100,0; 93,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,72; 127,95</t>
+          <t>-78,61; 115,62</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,68</t>
+          <t>-0,07; 0,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,04</t>
+          <t>-0,45; 0,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,46</t>
+          <t>-0,31; 0,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; -0,03</t>
+          <t>-0,66; 0,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,15</t>
+          <t>-0,56; 0,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,46</t>
+          <t>-0,12; 0,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; -0,07</t>
+          <t>-0,54; -0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,21</t>
+          <t>-0,26; 0,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 358,4</t>
+          <t>-20,4; 370,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-90,67; 63,55</t>
+          <t>-89,8; 61,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 261,77</t>
+          <t>-48,83; 237,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,55; 131,81</t>
+          <t>-44,28; 136,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,77; 10,18</t>
+          <t>-86,43; 31,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,39; 62,7</t>
+          <t>-67,55; 46,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 143,18</t>
+          <t>-22,97; 137,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-81,0; -17,02</t>
+          <t>-84,5; -11,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 68,51</t>
+          <t>-46,64; 71,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C08-Estudios-trans_camb.xlsx
@@ -649,22 +649,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>-0,3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,35</t>
+          <t>-0,32; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,48</t>
+          <t>-0,42; 1,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,14</t>
+          <t>-1,1; -0,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,39</t>
+          <t>-0,83; 0,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,55</t>
+          <t>-0,82; 0,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,1</t>
+          <t>-0,82; 0,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,56</t>
+          <t>-0,46; 0,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,64</t>
+          <t>-0,48; 0,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; -0,03</t>
+          <t>-0,76; 0,04</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-55,1%</t>
+          <t>-41,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-70,14%</t>
+          <t>-61,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-76,26; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 248,88</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 365,64</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,69; 80,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 239,18</t>
+          <t>-67,36; 228,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,31; 296,83</t>
+          <t>-74,74; 252,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,94; 38,94</t>
+          <t>-92,23; 62,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,09</t>
+          <t>0,14; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,0</t>
+          <t>-0,44; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,12</t>
+          <t>0,26; 1,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,94</t>
+          <t>-0,3; 0,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; -0,13</t>
+          <t>-1,01; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,18</t>
+          <t>-0,61; 0,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,76</t>
+          <t>0,06; 0,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,47</t>
+          <t>-0,06; 0,62</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>696,16%</t>
+          <t>903,43%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,11%</t>
+          <t>-22,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 389,92</t>
+          <t>-50,23; 426,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 103,68</t>
+          <t>-74,42; 145,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 603,2</t>
+          <t>-4,33; 643,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 11,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 359,46</t>
+          <t>-21,34; 421,29</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,82</t>
+          <t>-1,4; 0,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,01</t>
+          <t>-1,86; 0,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,06</t>
+          <t>-1,99; 0,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,62</t>
+          <t>-1,52; 0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,86</t>
+          <t>-1,32; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,08</t>
+          <t>-1,19; 1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,47</t>
+          <t>-1,09; 0,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,22</t>
+          <t>-1,24; 0,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,34</t>
+          <t>-1,06; 0,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-69,43%</t>
+          <t>-69,23%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-37,12%</t>
+          <t>-36,49%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 279,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 61,25</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,34; —</t>
+          <t>-80,78; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,37; 102,31</t>
+          <t>-82,57; 148,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,66</t>
+          <t>-100,0; 88,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 115,62</t>
+          <t>-78,75; 103,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 0,72</t>
+          <t>-0,13; 0,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,08</t>
+          <t>-0,47; 0,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,49</t>
+          <t>-0,13; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,46</t>
+          <t>-0,36; 0,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,03</t>
+          <t>-0,69; -0,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,13</t>
+          <t>-0,49; 0,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,46</t>
+          <t>-0,13; 0,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; -0,07</t>
+          <t>-0,48; -0,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,22</t>
+          <t>-0,2; 0,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,88%</t>
+          <t>-17,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,59%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 370,45</t>
+          <t>-34,8; 315,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,8; 61,96</t>
+          <t>-91,34; 49,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 237,43</t>
+          <t>-36,44; 323,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 136,07</t>
+          <t>-44,85; 136,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,43; 31,91</t>
+          <t>-89,4; 15,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 46,41</t>
+          <t>-62,37; 60,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 137,36</t>
+          <t>-22,55; 136,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,5; -11,14</t>
+          <t>-82,36; -8,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 71,99</t>
+          <t>-34,75; 93,48</t>
         </is>
       </c>
     </row>
